--- a/backend/src/main/resources/templates/annuel/GRAND_RECAP_CONGES_VALORISES.xlsx
+++ b/backend/src/main/resources/templates/annuel/GRAND_RECAP_CONGES_VALORISES.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -67,8 +67,20 @@
       <color rgb="00595959"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF07324A"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF07324A"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -120,8 +132,32 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF07324A"/>
+        <bgColor rgb="FF07324A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0C4C67"/>
+        <bgColor rgb="FF0C4C67"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1EDF2"/>
+        <bgColor rgb="FFE1EDF2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7F9FA"/>
+        <bgColor rgb="FFF7F9FA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -143,11 +179,55 @@
         <color rgb="00B8CCE4"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B8CCE4"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B8CCE4"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B8CCE4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -179,6 +259,29 @@
     <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -569,124 +672,124 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>GALAXAM — GRAND RÉCAPITULATIF DES CONGÉS VALORISÉS</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>Période / date de situation : ____________________    |    Synthèse par salarié des droits, mouvements, solde et valorisation</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>Matricule</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Nom &amp; prénom</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>Filiale</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Poste</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>Solde
 ouverture (j)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="13" t="inlineStr">
         <is>
           <t>Droits
 acquis (j)</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="13" t="inlineStr">
         <is>
           <t>Bonifi-
 cations (j)</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>Ajuste-
 ments nets (j)</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="13" t="inlineStr">
         <is>
           <t>Congés
 pris (j)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="K3" s="13" t="inlineStr">
         <is>
           <t>Expi-
 rations (j)</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="L3" s="13" t="inlineStr">
         <is>
           <t>Annul. /
 restitutions (j)</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="M3" s="13" t="inlineStr">
         <is>
           <t>Solde
 dispo. (j)</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="N3" s="13" t="inlineStr">
         <is>
           <t>TCONGE
 applicable (Ar/j)</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" s="13" t="inlineStr">
         <is>
           <t>Valeur du
 solde FIFO (Ar)</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="P3" s="13" t="inlineStr">
         <is>
           <t>Cumul valo.
 acquise (Ar)</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
+      <c r="Q3" s="13" t="inlineStr">
         <is>
           <t>Solde × TCONGE
 estimation (Ar)</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
+      <c r="R3" s="13" t="inlineStr">
         <is>
           <t>Période de
 référence</t>
         </is>
       </c>
-      <c r="S3" s="3" t="inlineStr">
+      <c r="S3" s="13" t="inlineStr">
         <is>
           <t>Statut
 période</t>
@@ -694,73 +797,73 @@
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>TOTAL GÉNÉRAL</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6">
+      <c r="B4" s="15" t="n"/>
+      <c r="C4" s="15" t="n"/>
+      <c r="D4" s="15" t="n"/>
+      <c r="E4" s="15" t="n"/>
+      <c r="F4" s="15">
         <f>SUM(F5:F104)</f>
         <v/>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="15">
         <f>SUM(G5:G104)</f>
         <v/>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="15">
         <f>SUM(H5:H104)</f>
         <v/>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="15">
         <f>SUM(I5:I104)</f>
         <v/>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="15">
         <f>SUM(J5:J104)</f>
         <v/>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="15">
         <f>SUM(K5:K104)</f>
         <v/>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="15">
         <f>SUM(L5:L104)</f>
         <v/>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="15">
         <f>SUM(M5:M104)</f>
         <v/>
       </c>
-      <c r="N4" s="6" t="inlineStr">
+      <c r="N4" s="15" t="inlineStr">
         <is>
           <t>— (voir détail)</t>
         </is>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="15">
         <f>SUM(O5:O104)</f>
         <v/>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="15">
         <f>SUM(P5:P104)</f>
         <v/>
       </c>
-      <c r="Q4" s="6">
+      <c r="Q4" s="15">
         <f>SUM(Q5:Q104)</f>
         <v/>
       </c>
-      <c r="R4" s="6" t="n"/>
-      <c r="S4" s="6" t="n"/>
+      <c r="R4" s="15" t="n"/>
+      <c r="S4" s="15" t="n"/>
     </row>
     <row r="5" ht="16" customHeight="1">
-      <c r="A5" s="7" t="n"/>
-      <c r="B5" s="7" t="n"/>
-      <c r="C5" s="7" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="7" t="n"/>
+      <c r="A5" s="16" t="n"/>
+      <c r="B5" s="16" t="n"/>
+      <c r="C5" s="16" t="n"/>
+      <c r="D5" s="16" t="n"/>
+      <c r="E5" s="16" t="n"/>
       <c r="F5" s="8" t="n"/>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="8" t="n"/>
@@ -771,17 +874,17 @@
       <c r="M5" s="8" t="n"/>
       <c r="N5" s="8" t="n"/>
       <c r="O5" s="8" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="9" t="n"/>
+      <c r="P5" s="17" t="n"/>
+      <c r="Q5" s="17" t="n"/>
       <c r="R5" s="8" t="n"/>
       <c r="S5" s="8" t="n"/>
     </row>
     <row r="6" ht="16" customHeight="1">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="A6" s="16" t="n"/>
+      <c r="B6" s="16" t="n"/>
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="16" t="n"/>
+      <c r="E6" s="16" t="n"/>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
       <c r="H6" s="8" t="n"/>
@@ -792,17 +895,17 @@
       <c r="M6" s="8" t="n"/>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="9" t="n"/>
+      <c r="P6" s="17" t="n"/>
+      <c r="Q6" s="17" t="n"/>
       <c r="R6" s="8" t="n"/>
       <c r="S6" s="8" t="n"/>
     </row>
     <row r="7" ht="16" customHeight="1">
-      <c r="A7" s="7" t="n"/>
-      <c r="B7" s="7" t="n"/>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
+      <c r="A7" s="16" t="n"/>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="16" t="n"/>
+      <c r="D7" s="16" t="n"/>
+      <c r="E7" s="16" t="n"/>
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="8" t="n"/>
@@ -813,17 +916,17 @@
       <c r="M7" s="8" t="n"/>
       <c r="N7" s="8" t="n"/>
       <c r="O7" s="8" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
       <c r="R7" s="8" t="n"/>
       <c r="S7" s="8" t="n"/>
     </row>
     <row r="8" ht="16" customHeight="1">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="7" t="n"/>
-      <c r="D8" s="7" t="n"/>
-      <c r="E8" s="7" t="n"/>
+      <c r="A8" s="16" t="n"/>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="16" t="n"/>
+      <c r="D8" s="16" t="n"/>
+      <c r="E8" s="16" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
@@ -834,17 +937,17 @@
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="8" t="n"/>
       <c r="O8" s="8" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
+      <c r="P8" s="17" t="n"/>
+      <c r="Q8" s="17" t="n"/>
       <c r="R8" s="8" t="n"/>
       <c r="S8" s="8" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="7" t="n"/>
-      <c r="C9" s="7" t="n"/>
-      <c r="D9" s="7" t="n"/>
-      <c r="E9" s="7" t="n"/>
+      <c r="A9" s="16" t="n"/>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="16" t="n"/>
+      <c r="E9" s="16" t="n"/>
       <c r="F9" s="8" t="n"/>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="8" t="n"/>
@@ -855,17 +958,17 @@
       <c r="M9" s="8" t="n"/>
       <c r="N9" s="8" t="n"/>
       <c r="O9" s="8" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
+      <c r="P9" s="17" t="n"/>
+      <c r="Q9" s="17" t="n"/>
       <c r="R9" s="8" t="n"/>
       <c r="S9" s="8" t="n"/>
     </row>
     <row r="10" ht="16" customHeight="1">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="7" t="n"/>
-      <c r="D10" s="7" t="n"/>
-      <c r="E10" s="7" t="n"/>
+      <c r="A10" s="16" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
@@ -876,17 +979,17 @@
       <c r="M10" s="8" t="n"/>
       <c r="N10" s="8" t="n"/>
       <c r="O10" s="8" t="n"/>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="9" t="n"/>
+      <c r="P10" s="17" t="n"/>
+      <c r="Q10" s="17" t="n"/>
       <c r="R10" s="8" t="n"/>
       <c r="S10" s="8" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="n"/>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
+      <c r="A11" s="16" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
       <c r="F11" s="8" t="n"/>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="8" t="n"/>
@@ -897,17 +1000,17 @@
       <c r="M11" s="8" t="n"/>
       <c r="N11" s="8" t="n"/>
       <c r="O11" s="8" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
+      <c r="P11" s="17" t="n"/>
+      <c r="Q11" s="17" t="n"/>
       <c r="R11" s="8" t="n"/>
       <c r="S11" s="8" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="7" t="n"/>
-      <c r="C12" s="7" t="n"/>
-      <c r="D12" s="7" t="n"/>
-      <c r="E12" s="7" t="n"/>
+      <c r="A12" s="16" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="8" t="n"/>
@@ -918,17 +1021,17 @@
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
       <c r="O12" s="8" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
+      <c r="P12" s="17" t="n"/>
+      <c r="Q12" s="17" t="n"/>
       <c r="R12" s="8" t="n"/>
       <c r="S12" s="8" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
-      <c r="A13" s="7" t="n"/>
-      <c r="B13" s="7" t="n"/>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
-      <c r="E13" s="7" t="n"/>
+      <c r="A13" s="16" t="n"/>
+      <c r="B13" s="16" t="n"/>
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="16" t="n"/>
       <c r="F13" s="8" t="n"/>
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="8" t="n"/>
@@ -939,17 +1042,17 @@
       <c r="M13" s="8" t="n"/>
       <c r="N13" s="8" t="n"/>
       <c r="O13" s="8" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="9" t="n"/>
+      <c r="P13" s="17" t="n"/>
+      <c r="Q13" s="17" t="n"/>
       <c r="R13" s="8" t="n"/>
       <c r="S13" s="8" t="n"/>
     </row>
     <row r="14" ht="16" customHeight="1">
-      <c r="A14" s="7" t="n"/>
-      <c r="B14" s="7" t="n"/>
-      <c r="C14" s="7" t="n"/>
-      <c r="D14" s="7" t="n"/>
-      <c r="E14" s="7" t="n"/>
+      <c r="A14" s="16" t="n"/>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="16" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
@@ -960,17 +1063,17 @@
       <c r="M14" s="8" t="n"/>
       <c r="N14" s="8" t="n"/>
       <c r="O14" s="8" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
+      <c r="P14" s="17" t="n"/>
+      <c r="Q14" s="17" t="n"/>
       <c r="R14" s="8" t="n"/>
       <c r="S14" s="8" t="n"/>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="7" t="n"/>
-      <c r="B15" s="7" t="n"/>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
+      <c r="A15" s="16" t="n"/>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="16" t="n"/>
       <c r="F15" s="8" t="n"/>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="8" t="n"/>
@@ -981,17 +1084,17 @@
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n"/>
       <c r="O15" s="8" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
+      <c r="P15" s="17" t="n"/>
+      <c r="Q15" s="17" t="n"/>
       <c r="R15" s="8" t="n"/>
       <c r="S15" s="8" t="n"/>
     </row>
     <row r="16" ht="16" customHeight="1">
-      <c r="A16" s="7" t="n"/>
-      <c r="B16" s="7" t="n"/>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
+      <c r="A16" s="16" t="n"/>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="16" t="n"/>
+      <c r="E16" s="16" t="n"/>
       <c r="F16" s="8" t="n"/>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -1002,17 +1105,17 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="9" t="n"/>
+      <c r="P16" s="17" t="n"/>
+      <c r="Q16" s="17" t="n"/>
       <c r="R16" s="8" t="n"/>
       <c r="S16" s="8" t="n"/>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="7" t="n"/>
-      <c r="B17" s="7" t="n"/>
-      <c r="C17" s="7" t="n"/>
-      <c r="D17" s="7" t="n"/>
-      <c r="E17" s="7" t="n"/>
+      <c r="A17" s="16" t="n"/>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="16" t="n"/>
+      <c r="E17" s="16" t="n"/>
       <c r="F17" s="8" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
@@ -1023,17 +1126,17 @@
       <c r="M17" s="8" t="n"/>
       <c r="N17" s="8" t="n"/>
       <c r="O17" s="8" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
+      <c r="P17" s="17" t="n"/>
+      <c r="Q17" s="17" t="n"/>
       <c r="R17" s="8" t="n"/>
       <c r="S17" s="8" t="n"/>
     </row>
     <row r="18" ht="16" customHeight="1">
-      <c r="A18" s="7" t="n"/>
-      <c r="B18" s="7" t="n"/>
-      <c r="C18" s="7" t="n"/>
-      <c r="D18" s="7" t="n"/>
-      <c r="E18" s="7" t="n"/>
+      <c r="A18" s="16" t="n"/>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="16" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
@@ -1044,17 +1147,17 @@
       <c r="M18" s="8" t="n"/>
       <c r="N18" s="8" t="n"/>
       <c r="O18" s="8" t="n"/>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="9" t="n"/>
+      <c r="P18" s="17" t="n"/>
+      <c r="Q18" s="17" t="n"/>
       <c r="R18" s="8" t="n"/>
       <c r="S18" s="8" t="n"/>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="7" t="n"/>
-      <c r="B19" s="7" t="n"/>
-      <c r="C19" s="7" t="n"/>
-      <c r="D19" s="7" t="n"/>
-      <c r="E19" s="7" t="n"/>
+      <c r="A19" s="16" t="n"/>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="8" t="n"/>
@@ -1065,17 +1168,17 @@
       <c r="M19" s="8" t="n"/>
       <c r="N19" s="8" t="n"/>
       <c r="O19" s="8" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
+      <c r="P19" s="17" t="n"/>
+      <c r="Q19" s="17" t="n"/>
       <c r="R19" s="8" t="n"/>
       <c r="S19" s="8" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="n"/>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="7" t="n"/>
+      <c r="A20" s="16" t="n"/>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
@@ -1086,17 +1189,17 @@
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="9" t="n"/>
+      <c r="P20" s="17" t="n"/>
+      <c r="Q20" s="17" t="n"/>
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="n"/>
-      <c r="C21" s="7" t="n"/>
-      <c r="D21" s="7" t="n"/>
-      <c r="E21" s="7" t="n"/>
+      <c r="A21" s="16" t="n"/>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="n"/>
+      <c r="E21" s="16" t="n"/>
       <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="8" t="n"/>
@@ -1107,17 +1210,17 @@
       <c r="M21" s="8" t="n"/>
       <c r="N21" s="8" t="n"/>
       <c r="O21" s="8" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
+      <c r="P21" s="17" t="n"/>
+      <c r="Q21" s="17" t="n"/>
       <c r="R21" s="8" t="n"/>
       <c r="S21" s="8" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1">
-      <c r="A22" s="7" t="n"/>
-      <c r="B22" s="7" t="n"/>
-      <c r="C22" s="7" t="n"/>
-      <c r="D22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
+      <c r="A22" s="16" t="n"/>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="n"/>
+      <c r="E22" s="16" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
@@ -1128,17 +1231,17 @@
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
+      <c r="P22" s="17" t="n"/>
+      <c r="Q22" s="17" t="n"/>
       <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="n"/>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="7" t="n"/>
-      <c r="B23" s="7" t="n"/>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
+      <c r="A23" s="16" t="n"/>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="n"/>
+      <c r="E23" s="16" t="n"/>
       <c r="F23" s="8" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="8" t="n"/>
@@ -1149,17 +1252,17 @@
       <c r="M23" s="8" t="n"/>
       <c r="N23" s="8" t="n"/>
       <c r="O23" s="8" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
+      <c r="P23" s="17" t="n"/>
+      <c r="Q23" s="17" t="n"/>
       <c r="R23" s="8" t="n"/>
       <c r="S23" s="8" t="n"/>
     </row>
     <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="7" t="n"/>
-      <c r="B24" s="7" t="n"/>
-      <c r="C24" s="7" t="n"/>
-      <c r="D24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
+      <c r="A24" s="16" t="n"/>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="n"/>
+      <c r="E24" s="16" t="n"/>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
@@ -1170,17 +1273,17 @@
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
       <c r="O24" s="8" t="n"/>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="9" t="n"/>
+      <c r="P24" s="17" t="n"/>
+      <c r="Q24" s="17" t="n"/>
       <c r="R24" s="8" t="n"/>
       <c r="S24" s="8" t="n"/>
     </row>
     <row r="25" ht="16" customHeight="1">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="n"/>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-      <c r="E25" s="7" t="n"/>
+      <c r="A25" s="16" t="n"/>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="n"/>
+      <c r="E25" s="16" t="n"/>
       <c r="F25" s="8" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="8" t="n"/>
@@ -1191,17 +1294,17 @@
       <c r="M25" s="8" t="n"/>
       <c r="N25" s="8" t="n"/>
       <c r="O25" s="8" t="n"/>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="9" t="n"/>
+      <c r="P25" s="17" t="n"/>
+      <c r="Q25" s="17" t="n"/>
       <c r="R25" s="8" t="n"/>
       <c r="S25" s="8" t="n"/>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="7" t="n"/>
-      <c r="B26" s="7" t="n"/>
-      <c r="C26" s="7" t="n"/>
-      <c r="D26" s="7" t="n"/>
-      <c r="E26" s="7" t="n"/>
+      <c r="A26" s="16" t="n"/>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="n"/>
+      <c r="E26" s="16" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
@@ -1212,17 +1315,17 @@
       <c r="M26" s="8" t="n"/>
       <c r="N26" s="8" t="n"/>
       <c r="O26" s="8" t="n"/>
-      <c r="P26" s="9" t="n"/>
-      <c r="Q26" s="9" t="n"/>
+      <c r="P26" s="17" t="n"/>
+      <c r="Q26" s="17" t="n"/>
       <c r="R26" s="8" t="n"/>
       <c r="S26" s="8" t="n"/>
     </row>
     <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="7" t="n"/>
-      <c r="B27" s="7" t="n"/>
-      <c r="C27" s="7" t="n"/>
-      <c r="D27" s="7" t="n"/>
-      <c r="E27" s="7" t="n"/>
+      <c r="A27" s="16" t="n"/>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="n"/>
+      <c r="E27" s="16" t="n"/>
       <c r="F27" s="8" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="8" t="n"/>
@@ -1233,17 +1336,17 @@
       <c r="M27" s="8" t="n"/>
       <c r="N27" s="8" t="n"/>
       <c r="O27" s="8" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
+      <c r="P27" s="17" t="n"/>
+      <c r="Q27" s="17" t="n"/>
       <c r="R27" s="8" t="n"/>
       <c r="S27" s="8" t="n"/>
     </row>
     <row r="28" ht="16" customHeight="1">
-      <c r="A28" s="7" t="n"/>
-      <c r="B28" s="7" t="n"/>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
-      <c r="E28" s="7" t="n"/>
+      <c r="A28" s="16" t="n"/>
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="n"/>
+      <c r="E28" s="16" t="n"/>
       <c r="F28" s="8" t="n"/>
       <c r="G28" s="8" t="n"/>
       <c r="H28" s="8" t="n"/>
@@ -1254,17 +1357,17 @@
       <c r="M28" s="8" t="n"/>
       <c r="N28" s="8" t="n"/>
       <c r="O28" s="8" t="n"/>
-      <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="9" t="n"/>
+      <c r="P28" s="17" t="n"/>
+      <c r="Q28" s="17" t="n"/>
       <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n"/>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="7" t="n"/>
-      <c r="B29" s="7" t="n"/>
-      <c r="C29" s="7" t="n"/>
-      <c r="D29" s="7" t="n"/>
-      <c r="E29" s="7" t="n"/>
+      <c r="A29" s="16" t="n"/>
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="n"/>
+      <c r="E29" s="16" t="n"/>
       <c r="F29" s="8" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="8" t="n"/>
@@ -1275,17 +1378,17 @@
       <c r="M29" s="8" t="n"/>
       <c r="N29" s="8" t="n"/>
       <c r="O29" s="8" t="n"/>
-      <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
+      <c r="P29" s="17" t="n"/>
+      <c r="Q29" s="17" t="n"/>
       <c r="R29" s="8" t="n"/>
       <c r="S29" s="8" t="n"/>
     </row>
     <row r="30" ht="16" customHeight="1">
-      <c r="A30" s="7" t="n"/>
-      <c r="B30" s="7" t="n"/>
-      <c r="C30" s="7" t="n"/>
-      <c r="D30" s="7" t="n"/>
-      <c r="E30" s="7" t="n"/>
+      <c r="A30" s="16" t="n"/>
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="16" t="n"/>
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="n"/>
       <c r="H30" s="8" t="n"/>
@@ -1296,17 +1399,17 @@
       <c r="M30" s="8" t="n"/>
       <c r="N30" s="8" t="n"/>
       <c r="O30" s="8" t="n"/>
-      <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
+      <c r="P30" s="17" t="n"/>
+      <c r="Q30" s="17" t="n"/>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
     </row>
     <row r="31" ht="16" customHeight="1">
-      <c r="A31" s="7" t="n"/>
-      <c r="B31" s="7" t="n"/>
-      <c r="C31" s="7" t="n"/>
-      <c r="D31" s="7" t="n"/>
-      <c r="E31" s="7" t="n"/>
+      <c r="A31" s="16" t="n"/>
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="n"/>
+      <c r="E31" s="16" t="n"/>
       <c r="F31" s="8" t="n"/>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="8" t="n"/>
@@ -1317,17 +1420,17 @@
       <c r="M31" s="8" t="n"/>
       <c r="N31" s="8" t="n"/>
       <c r="O31" s="8" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
+      <c r="P31" s="17" t="n"/>
+      <c r="Q31" s="17" t="n"/>
       <c r="R31" s="8" t="n"/>
       <c r="S31" s="8" t="n"/>
     </row>
     <row r="32" ht="16" customHeight="1">
-      <c r="A32" s="7" t="n"/>
-      <c r="B32" s="7" t="n"/>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
+      <c r="A32" s="16" t="n"/>
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="n"/>
+      <c r="E32" s="16" t="n"/>
       <c r="F32" s="8" t="n"/>
       <c r="G32" s="8" t="n"/>
       <c r="H32" s="8" t="n"/>
@@ -1338,17 +1441,17 @@
       <c r="M32" s="8" t="n"/>
       <c r="N32" s="8" t="n"/>
       <c r="O32" s="8" t="n"/>
-      <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
+      <c r="P32" s="17" t="n"/>
+      <c r="Q32" s="17" t="n"/>
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="7" t="n"/>
-      <c r="B33" s="7" t="n"/>
-      <c r="C33" s="7" t="n"/>
-      <c r="D33" s="7" t="n"/>
-      <c r="E33" s="7" t="n"/>
+      <c r="A33" s="16" t="n"/>
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="n"/>
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="n"/>
       <c r="H33" s="8" t="n"/>
@@ -1359,17 +1462,17 @@
       <c r="M33" s="8" t="n"/>
       <c r="N33" s="8" t="n"/>
       <c r="O33" s="8" t="n"/>
-      <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
+      <c r="P33" s="17" t="n"/>
+      <c r="Q33" s="17" t="n"/>
       <c r="R33" s="8" t="n"/>
       <c r="S33" s="8" t="n"/>
     </row>
     <row r="34" ht="16" customHeight="1">
-      <c r="A34" s="7" t="n"/>
-      <c r="B34" s="7" t="n"/>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
-      <c r="E34" s="7" t="n"/>
+      <c r="A34" s="16" t="n"/>
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="n"/>
       <c r="F34" s="8" t="n"/>
       <c r="G34" s="8" t="n"/>
       <c r="H34" s="8" t="n"/>
@@ -1380,17 +1483,17 @@
       <c r="M34" s="8" t="n"/>
       <c r="N34" s="8" t="n"/>
       <c r="O34" s="8" t="n"/>
-      <c r="P34" s="9" t="n"/>
-      <c r="Q34" s="9" t="n"/>
+      <c r="P34" s="17" t="n"/>
+      <c r="Q34" s="17" t="n"/>
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n"/>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="7" t="n"/>
-      <c r="B35" s="7" t="n"/>
-      <c r="C35" s="7" t="n"/>
-      <c r="D35" s="7" t="n"/>
-      <c r="E35" s="7" t="n"/>
+      <c r="A35" s="16" t="n"/>
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="n"/>
       <c r="F35" s="8" t="n"/>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="8" t="n"/>
@@ -1401,17 +1504,17 @@
       <c r="M35" s="8" t="n"/>
       <c r="N35" s="8" t="n"/>
       <c r="O35" s="8" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
+      <c r="P35" s="17" t="n"/>
+      <c r="Q35" s="17" t="n"/>
       <c r="R35" s="8" t="n"/>
       <c r="S35" s="8" t="n"/>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="7" t="n"/>
-      <c r="B36" s="7" t="n"/>
-      <c r="C36" s="7" t="n"/>
-      <c r="D36" s="7" t="n"/>
-      <c r="E36" s="7" t="n"/>
+      <c r="A36" s="16" t="n"/>
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="n"/>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
       <c r="F36" s="8" t="n"/>
       <c r="G36" s="8" t="n"/>
       <c r="H36" s="8" t="n"/>
@@ -1422,17 +1525,17 @@
       <c r="M36" s="8" t="n"/>
       <c r="N36" s="8" t="n"/>
       <c r="O36" s="8" t="n"/>
-      <c r="P36" s="9" t="n"/>
-      <c r="Q36" s="9" t="n"/>
+      <c r="P36" s="17" t="n"/>
+      <c r="Q36" s="17" t="n"/>
       <c r="R36" s="8" t="n"/>
       <c r="S36" s="8" t="n"/>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="7" t="n"/>
-      <c r="B37" s="7" t="n"/>
-      <c r="C37" s="7" t="n"/>
-      <c r="D37" s="7" t="n"/>
-      <c r="E37" s="7" t="n"/>
+      <c r="A37" s="16" t="n"/>
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
       <c r="F37" s="8" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="8" t="n"/>
@@ -1443,17 +1546,17 @@
       <c r="M37" s="8" t="n"/>
       <c r="N37" s="8" t="n"/>
       <c r="O37" s="8" t="n"/>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
+      <c r="P37" s="17" t="n"/>
+      <c r="Q37" s="17" t="n"/>
       <c r="R37" s="8" t="n"/>
       <c r="S37" s="8" t="n"/>
     </row>
     <row r="38" ht="16" customHeight="1">
-      <c r="A38" s="7" t="n"/>
-      <c r="B38" s="7" t="n"/>
-      <c r="C38" s="7" t="n"/>
-      <c r="D38" s="7" t="n"/>
-      <c r="E38" s="7" t="n"/>
+      <c r="A38" s="16" t="n"/>
+      <c r="B38" s="16" t="n"/>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
       <c r="F38" s="8" t="n"/>
       <c r="G38" s="8" t="n"/>
       <c r="H38" s="8" t="n"/>
@@ -1464,17 +1567,17 @@
       <c r="M38" s="8" t="n"/>
       <c r="N38" s="8" t="n"/>
       <c r="O38" s="8" t="n"/>
-      <c r="P38" s="9" t="n"/>
-      <c r="Q38" s="9" t="n"/>
+      <c r="P38" s="17" t="n"/>
+      <c r="Q38" s="17" t="n"/>
       <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="n"/>
     </row>
     <row r="39" ht="16" customHeight="1">
-      <c r="A39" s="7" t="n"/>
-      <c r="B39" s="7" t="n"/>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
+      <c r="A39" s="16" t="n"/>
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
       <c r="F39" s="8" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="8" t="n"/>
@@ -1485,17 +1588,17 @@
       <c r="M39" s="8" t="n"/>
       <c r="N39" s="8" t="n"/>
       <c r="O39" s="8" t="n"/>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
+      <c r="P39" s="17" t="n"/>
+      <c r="Q39" s="17" t="n"/>
       <c r="R39" s="8" t="n"/>
       <c r="S39" s="8" t="n"/>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="7" t="n"/>
-      <c r="B40" s="7" t="n"/>
-      <c r="C40" s="7" t="n"/>
-      <c r="D40" s="7" t="n"/>
-      <c r="E40" s="7" t="n"/>
+      <c r="A40" s="16" t="n"/>
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
       <c r="F40" s="8" t="n"/>
       <c r="G40" s="8" t="n"/>
       <c r="H40" s="8" t="n"/>
@@ -1506,17 +1609,17 @@
       <c r="M40" s="8" t="n"/>
       <c r="N40" s="8" t="n"/>
       <c r="O40" s="8" t="n"/>
-      <c r="P40" s="9" t="n"/>
-      <c r="Q40" s="9" t="n"/>
+      <c r="P40" s="17" t="n"/>
+      <c r="Q40" s="17" t="n"/>
       <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="n"/>
     </row>
     <row r="41" ht="16" customHeight="1">
-      <c r="A41" s="7" t="n"/>
-      <c r="B41" s="7" t="n"/>
-      <c r="C41" s="7" t="n"/>
-      <c r="D41" s="7" t="n"/>
-      <c r="E41" s="7" t="n"/>
+      <c r="A41" s="16" t="n"/>
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
       <c r="F41" s="8" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="8" t="n"/>
@@ -1527,17 +1630,17 @@
       <c r="M41" s="8" t="n"/>
       <c r="N41" s="8" t="n"/>
       <c r="O41" s="8" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
+      <c r="P41" s="17" t="n"/>
+      <c r="Q41" s="17" t="n"/>
       <c r="R41" s="8" t="n"/>
       <c r="S41" s="8" t="n"/>
     </row>
     <row r="42" ht="16" customHeight="1">
-      <c r="A42" s="7" t="n"/>
-      <c r="B42" s="7" t="n"/>
-      <c r="C42" s="7" t="n"/>
-      <c r="D42" s="7" t="n"/>
-      <c r="E42" s="7" t="n"/>
+      <c r="A42" s="16" t="n"/>
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
       <c r="F42" s="8" t="n"/>
       <c r="G42" s="8" t="n"/>
       <c r="H42" s="8" t="n"/>
@@ -1548,17 +1651,17 @@
       <c r="M42" s="8" t="n"/>
       <c r="N42" s="8" t="n"/>
       <c r="O42" s="8" t="n"/>
-      <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="9" t="n"/>
+      <c r="P42" s="17" t="n"/>
+      <c r="Q42" s="17" t="n"/>
       <c r="R42" s="8" t="n"/>
       <c r="S42" s="8" t="n"/>
     </row>
     <row r="43" ht="16" customHeight="1">
-      <c r="A43" s="7" t="n"/>
-      <c r="B43" s="7" t="n"/>
-      <c r="C43" s="7" t="n"/>
-      <c r="D43" s="7" t="n"/>
-      <c r="E43" s="7" t="n"/>
+      <c r="A43" s="16" t="n"/>
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
       <c r="F43" s="8" t="n"/>
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="8" t="n"/>
@@ -1569,17 +1672,17 @@
       <c r="M43" s="8" t="n"/>
       <c r="N43" s="8" t="n"/>
       <c r="O43" s="8" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
+      <c r="P43" s="17" t="n"/>
+      <c r="Q43" s="17" t="n"/>
       <c r="R43" s="8" t="n"/>
       <c r="S43" s="8" t="n"/>
     </row>
     <row r="44" ht="16" customHeight="1">
-      <c r="A44" s="7" t="n"/>
-      <c r="B44" s="7" t="n"/>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
+      <c r="A44" s="16" t="n"/>
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="n"/>
       <c r="H44" s="8" t="n"/>
@@ -1590,17 +1693,17 @@
       <c r="M44" s="8" t="n"/>
       <c r="N44" s="8" t="n"/>
       <c r="O44" s="8" t="n"/>
-      <c r="P44" s="9" t="n"/>
-      <c r="Q44" s="9" t="n"/>
+      <c r="P44" s="17" t="n"/>
+      <c r="Q44" s="17" t="n"/>
       <c r="R44" s="8" t="n"/>
       <c r="S44" s="8" t="n"/>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="7" t="n"/>
-      <c r="B45" s="7" t="n"/>
-      <c r="C45" s="7" t="n"/>
-      <c r="D45" s="7" t="n"/>
-      <c r="E45" s="7" t="n"/>
+      <c r="A45" s="16" t="n"/>
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="n"/>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="n"/>
       <c r="H45" s="8" t="n"/>
@@ -1611,17 +1714,17 @@
       <c r="M45" s="8" t="n"/>
       <c r="N45" s="8" t="n"/>
       <c r="O45" s="8" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
+      <c r="P45" s="17" t="n"/>
+      <c r="Q45" s="17" t="n"/>
       <c r="R45" s="8" t="n"/>
       <c r="S45" s="8" t="n"/>
     </row>
     <row r="46" ht="16" customHeight="1">
-      <c r="A46" s="7" t="n"/>
-      <c r="B46" s="7" t="n"/>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
-      <c r="E46" s="7" t="n"/>
+      <c r="A46" s="16" t="n"/>
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
       <c r="F46" s="8" t="n"/>
       <c r="G46" s="8" t="n"/>
       <c r="H46" s="8" t="n"/>
@@ -1632,17 +1735,17 @@
       <c r="M46" s="8" t="n"/>
       <c r="N46" s="8" t="n"/>
       <c r="O46" s="8" t="n"/>
-      <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="9" t="n"/>
+      <c r="P46" s="17" t="n"/>
+      <c r="Q46" s="17" t="n"/>
       <c r="R46" s="8" t="n"/>
       <c r="S46" s="8" t="n"/>
     </row>
     <row r="47" ht="16" customHeight="1">
-      <c r="A47" s="7" t="n"/>
-      <c r="B47" s="7" t="n"/>
-      <c r="C47" s="7" t="n"/>
-      <c r="D47" s="7" t="n"/>
-      <c r="E47" s="7" t="n"/>
+      <c r="A47" s="16" t="n"/>
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
       <c r="F47" s="8" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="8" t="n"/>
@@ -1653,17 +1756,17 @@
       <c r="M47" s="8" t="n"/>
       <c r="N47" s="8" t="n"/>
       <c r="O47" s="8" t="n"/>
-      <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
+      <c r="P47" s="17" t="n"/>
+      <c r="Q47" s="17" t="n"/>
       <c r="R47" s="8" t="n"/>
       <c r="S47" s="8" t="n"/>
     </row>
     <row r="48" ht="16" customHeight="1">
-      <c r="A48" s="7" t="n"/>
-      <c r="B48" s="7" t="n"/>
-      <c r="C48" s="7" t="n"/>
-      <c r="D48" s="7" t="n"/>
-      <c r="E48" s="7" t="n"/>
+      <c r="A48" s="16" t="n"/>
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="n"/>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
       <c r="F48" s="8" t="n"/>
       <c r="G48" s="8" t="n"/>
       <c r="H48" s="8" t="n"/>
@@ -1674,17 +1777,17 @@
       <c r="M48" s="8" t="n"/>
       <c r="N48" s="8" t="n"/>
       <c r="O48" s="8" t="n"/>
-      <c r="P48" s="9" t="n"/>
-      <c r="Q48" s="9" t="n"/>
+      <c r="P48" s="17" t="n"/>
+      <c r="Q48" s="17" t="n"/>
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n"/>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="7" t="n"/>
-      <c r="B49" s="7" t="n"/>
-      <c r="C49" s="7" t="n"/>
-      <c r="D49" s="7" t="n"/>
-      <c r="E49" s="7" t="n"/>
+      <c r="A49" s="16" t="n"/>
+      <c r="B49" s="16" t="n"/>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="16" t="n"/>
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="8" t="n"/>
@@ -1695,17 +1798,17 @@
       <c r="M49" s="8" t="n"/>
       <c r="N49" s="8" t="n"/>
       <c r="O49" s="8" t="n"/>
-      <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
+      <c r="P49" s="17" t="n"/>
+      <c r="Q49" s="17" t="n"/>
       <c r="R49" s="8" t="n"/>
       <c r="S49" s="8" t="n"/>
     </row>
     <row r="50" ht="16" customHeight="1">
-      <c r="A50" s="7" t="n"/>
-      <c r="B50" s="7" t="n"/>
-      <c r="C50" s="7" t="n"/>
-      <c r="D50" s="7" t="n"/>
-      <c r="E50" s="7" t="n"/>
+      <c r="A50" s="16" t="n"/>
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="16" t="n"/>
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="n"/>
       <c r="H50" s="8" t="n"/>
@@ -1716,17 +1819,17 @@
       <c r="M50" s="8" t="n"/>
       <c r="N50" s="8" t="n"/>
       <c r="O50" s="8" t="n"/>
-      <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="9" t="n"/>
+      <c r="P50" s="17" t="n"/>
+      <c r="Q50" s="17" t="n"/>
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n"/>
     </row>
     <row r="51" ht="16" customHeight="1">
-      <c r="A51" s="7" t="n"/>
-      <c r="B51" s="7" t="n"/>
-      <c r="C51" s="7" t="n"/>
-      <c r="D51" s="7" t="n"/>
-      <c r="E51" s="7" t="n"/>
+      <c r="A51" s="16" t="n"/>
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="n"/>
+      <c r="E51" s="16" t="n"/>
       <c r="F51" s="8" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="8" t="n"/>
@@ -1737,17 +1840,17 @@
       <c r="M51" s="8" t="n"/>
       <c r="N51" s="8" t="n"/>
       <c r="O51" s="8" t="n"/>
-      <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
+      <c r="P51" s="17" t="n"/>
+      <c r="Q51" s="17" t="n"/>
       <c r="R51" s="8" t="n"/>
       <c r="S51" s="8" t="n"/>
     </row>
     <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="7" t="n"/>
-      <c r="B52" s="7" t="n"/>
-      <c r="C52" s="7" t="n"/>
-      <c r="D52" s="7" t="n"/>
-      <c r="E52" s="7" t="n"/>
+      <c r="A52" s="16" t="n"/>
+      <c r="B52" s="16" t="n"/>
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="16" t="n"/>
+      <c r="E52" s="16" t="n"/>
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="n"/>
       <c r="H52" s="8" t="n"/>
@@ -1758,17 +1861,17 @@
       <c r="M52" s="8" t="n"/>
       <c r="N52" s="8" t="n"/>
       <c r="O52" s="8" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
+      <c r="P52" s="17" t="n"/>
+      <c r="Q52" s="17" t="n"/>
       <c r="R52" s="8" t="n"/>
       <c r="S52" s="8" t="n"/>
     </row>
     <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="7" t="n"/>
-      <c r="B53" s="7" t="n"/>
-      <c r="C53" s="7" t="n"/>
-      <c r="D53" s="7" t="n"/>
-      <c r="E53" s="7" t="n"/>
+      <c r="A53" s="16" t="n"/>
+      <c r="B53" s="16" t="n"/>
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="n"/>
+      <c r="E53" s="16" t="n"/>
       <c r="F53" s="8" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="8" t="n"/>
@@ -1779,17 +1882,17 @@
       <c r="M53" s="8" t="n"/>
       <c r="N53" s="8" t="n"/>
       <c r="O53" s="8" t="n"/>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
+      <c r="P53" s="17" t="n"/>
+      <c r="Q53" s="17" t="n"/>
       <c r="R53" s="8" t="n"/>
       <c r="S53" s="8" t="n"/>
     </row>
     <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="7" t="n"/>
-      <c r="B54" s="7" t="n"/>
-      <c r="C54" s="7" t="n"/>
-      <c r="D54" s="7" t="n"/>
-      <c r="E54" s="7" t="n"/>
+      <c r="A54" s="16" t="n"/>
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="n"/>
+      <c r="E54" s="16" t="n"/>
       <c r="F54" s="8" t="n"/>
       <c r="G54" s="8" t="n"/>
       <c r="H54" s="8" t="n"/>
@@ -1800,17 +1903,17 @@
       <c r="M54" s="8" t="n"/>
       <c r="N54" s="8" t="n"/>
       <c r="O54" s="8" t="n"/>
-      <c r="P54" s="9" t="n"/>
-      <c r="Q54" s="9" t="n"/>
+      <c r="P54" s="17" t="n"/>
+      <c r="Q54" s="17" t="n"/>
       <c r="R54" s="8" t="n"/>
       <c r="S54" s="8" t="n"/>
     </row>
     <row r="55" ht="16" customHeight="1">
-      <c r="A55" s="7" t="n"/>
-      <c r="B55" s="7" t="n"/>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
-      <c r="E55" s="7" t="n"/>
+      <c r="A55" s="16" t="n"/>
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="n"/>
+      <c r="E55" s="16" t="n"/>
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="8" t="n"/>
@@ -1821,17 +1924,17 @@
       <c r="M55" s="8" t="n"/>
       <c r="N55" s="8" t="n"/>
       <c r="O55" s="8" t="n"/>
-      <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="9" t="n"/>
+      <c r="P55" s="17" t="n"/>
+      <c r="Q55" s="17" t="n"/>
       <c r="R55" s="8" t="n"/>
       <c r="S55" s="8" t="n"/>
     </row>
     <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="7" t="n"/>
-      <c r="B56" s="7" t="n"/>
-      <c r="C56" s="7" t="n"/>
-      <c r="D56" s="7" t="n"/>
-      <c r="E56" s="7" t="n"/>
+      <c r="A56" s="16" t="n"/>
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="16" t="n"/>
       <c r="F56" s="8" t="n"/>
       <c r="G56" s="8" t="n"/>
       <c r="H56" s="8" t="n"/>
@@ -1842,17 +1945,17 @@
       <c r="M56" s="8" t="n"/>
       <c r="N56" s="8" t="n"/>
       <c r="O56" s="8" t="n"/>
-      <c r="P56" s="9" t="n"/>
-      <c r="Q56" s="9" t="n"/>
+      <c r="P56" s="17" t="n"/>
+      <c r="Q56" s="17" t="n"/>
       <c r="R56" s="8" t="n"/>
       <c r="S56" s="8" t="n"/>
     </row>
     <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="7" t="n"/>
-      <c r="B57" s="7" t="n"/>
-      <c r="C57" s="7" t="n"/>
-      <c r="D57" s="7" t="n"/>
-      <c r="E57" s="7" t="n"/>
+      <c r="A57" s="16" t="n"/>
+      <c r="B57" s="16" t="n"/>
+      <c r="C57" s="16" t="n"/>
+      <c r="D57" s="16" t="n"/>
+      <c r="E57" s="16" t="n"/>
       <c r="F57" s="8" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="8" t="n"/>
@@ -1863,17 +1966,17 @@
       <c r="M57" s="8" t="n"/>
       <c r="N57" s="8" t="n"/>
       <c r="O57" s="8" t="n"/>
-      <c r="P57" s="9" t="n"/>
-      <c r="Q57" s="9" t="n"/>
+      <c r="P57" s="17" t="n"/>
+      <c r="Q57" s="17" t="n"/>
       <c r="R57" s="8" t="n"/>
       <c r="S57" s="8" t="n"/>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="7" t="n"/>
-      <c r="B58" s="7" t="n"/>
-      <c r="C58" s="7" t="n"/>
-      <c r="D58" s="7" t="n"/>
-      <c r="E58" s="7" t="n"/>
+      <c r="A58" s="16" t="n"/>
+      <c r="B58" s="16" t="n"/>
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="16" t="n"/>
       <c r="F58" s="8" t="n"/>
       <c r="G58" s="8" t="n"/>
       <c r="H58" s="8" t="n"/>
@@ -1884,17 +1987,17 @@
       <c r="M58" s="8" t="n"/>
       <c r="N58" s="8" t="n"/>
       <c r="O58" s="8" t="n"/>
-      <c r="P58" s="9" t="n"/>
-      <c r="Q58" s="9" t="n"/>
+      <c r="P58" s="17" t="n"/>
+      <c r="Q58" s="17" t="n"/>
       <c r="R58" s="8" t="n"/>
       <c r="S58" s="8" t="n"/>
     </row>
     <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="7" t="n"/>
-      <c r="B59" s="7" t="n"/>
-      <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
-      <c r="E59" s="7" t="n"/>
+      <c r="A59" s="16" t="n"/>
+      <c r="B59" s="16" t="n"/>
+      <c r="C59" s="16" t="n"/>
+      <c r="D59" s="16" t="n"/>
+      <c r="E59" s="16" t="n"/>
       <c r="F59" s="8" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="8" t="n"/>
@@ -1905,17 +2008,17 @@
       <c r="M59" s="8" t="n"/>
       <c r="N59" s="8" t="n"/>
       <c r="O59" s="8" t="n"/>
-      <c r="P59" s="9" t="n"/>
-      <c r="Q59" s="9" t="n"/>
+      <c r="P59" s="17" t="n"/>
+      <c r="Q59" s="17" t="n"/>
       <c r="R59" s="8" t="n"/>
       <c r="S59" s="8" t="n"/>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="7" t="n"/>
-      <c r="B60" s="7" t="n"/>
-      <c r="C60" s="7" t="n"/>
-      <c r="D60" s="7" t="n"/>
-      <c r="E60" s="7" t="n"/>
+      <c r="A60" s="16" t="n"/>
+      <c r="B60" s="16" t="n"/>
+      <c r="C60" s="16" t="n"/>
+      <c r="D60" s="16" t="n"/>
+      <c r="E60" s="16" t="n"/>
       <c r="F60" s="8" t="n"/>
       <c r="G60" s="8" t="n"/>
       <c r="H60" s="8" t="n"/>
@@ -1926,17 +2029,17 @@
       <c r="M60" s="8" t="n"/>
       <c r="N60" s="8" t="n"/>
       <c r="O60" s="8" t="n"/>
-      <c r="P60" s="9" t="n"/>
-      <c r="Q60" s="9" t="n"/>
+      <c r="P60" s="17" t="n"/>
+      <c r="Q60" s="17" t="n"/>
       <c r="R60" s="8" t="n"/>
       <c r="S60" s="8" t="n"/>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="7" t="n"/>
-      <c r="B61" s="7" t="n"/>
-      <c r="C61" s="7" t="n"/>
-      <c r="D61" s="7" t="n"/>
-      <c r="E61" s="7" t="n"/>
+      <c r="A61" s="16" t="n"/>
+      <c r="B61" s="16" t="n"/>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="16" t="n"/>
+      <c r="E61" s="16" t="n"/>
       <c r="F61" s="8" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="8" t="n"/>
@@ -1947,17 +2050,17 @@
       <c r="M61" s="8" t="n"/>
       <c r="N61" s="8" t="n"/>
       <c r="O61" s="8" t="n"/>
-      <c r="P61" s="9" t="n"/>
-      <c r="Q61" s="9" t="n"/>
+      <c r="P61" s="17" t="n"/>
+      <c r="Q61" s="17" t="n"/>
       <c r="R61" s="8" t="n"/>
       <c r="S61" s="8" t="n"/>
     </row>
     <row r="62" ht="16" customHeight="1">
-      <c r="A62" s="7" t="n"/>
-      <c r="B62" s="7" t="n"/>
-      <c r="C62" s="7" t="n"/>
-      <c r="D62" s="7" t="n"/>
-      <c r="E62" s="7" t="n"/>
+      <c r="A62" s="16" t="n"/>
+      <c r="B62" s="16" t="n"/>
+      <c r="C62" s="16" t="n"/>
+      <c r="D62" s="16" t="n"/>
+      <c r="E62" s="16" t="n"/>
       <c r="F62" s="8" t="n"/>
       <c r="G62" s="8" t="n"/>
       <c r="H62" s="8" t="n"/>
@@ -1968,17 +2071,17 @@
       <c r="M62" s="8" t="n"/>
       <c r="N62" s="8" t="n"/>
       <c r="O62" s="8" t="n"/>
-      <c r="P62" s="9" t="n"/>
-      <c r="Q62" s="9" t="n"/>
+      <c r="P62" s="17" t="n"/>
+      <c r="Q62" s="17" t="n"/>
       <c r="R62" s="8" t="n"/>
       <c r="S62" s="8" t="n"/>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="7" t="n"/>
-      <c r="B63" s="7" t="n"/>
-      <c r="C63" s="7" t="n"/>
-      <c r="D63" s="7" t="n"/>
-      <c r="E63" s="7" t="n"/>
+      <c r="A63" s="16" t="n"/>
+      <c r="B63" s="16" t="n"/>
+      <c r="C63" s="16" t="n"/>
+      <c r="D63" s="16" t="n"/>
+      <c r="E63" s="16" t="n"/>
       <c r="F63" s="8" t="n"/>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="8" t="n"/>
@@ -1989,17 +2092,17 @@
       <c r="M63" s="8" t="n"/>
       <c r="N63" s="8" t="n"/>
       <c r="O63" s="8" t="n"/>
-      <c r="P63" s="9" t="n"/>
-      <c r="Q63" s="9" t="n"/>
+      <c r="P63" s="17" t="n"/>
+      <c r="Q63" s="17" t="n"/>
       <c r="R63" s="8" t="n"/>
       <c r="S63" s="8" t="n"/>
     </row>
     <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="7" t="n"/>
-      <c r="B64" s="7" t="n"/>
-      <c r="C64" s="7" t="n"/>
-      <c r="D64" s="7" t="n"/>
-      <c r="E64" s="7" t="n"/>
+      <c r="A64" s="16" t="n"/>
+      <c r="B64" s="16" t="n"/>
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="16" t="n"/>
       <c r="F64" s="8" t="n"/>
       <c r="G64" s="8" t="n"/>
       <c r="H64" s="8" t="n"/>
@@ -2010,17 +2113,17 @@
       <c r="M64" s="8" t="n"/>
       <c r="N64" s="8" t="n"/>
       <c r="O64" s="8" t="n"/>
-      <c r="P64" s="9" t="n"/>
-      <c r="Q64" s="9" t="n"/>
+      <c r="P64" s="17" t="n"/>
+      <c r="Q64" s="17" t="n"/>
       <c r="R64" s="8" t="n"/>
       <c r="S64" s="8" t="n"/>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="7" t="n"/>
-      <c r="B65" s="7" t="n"/>
-      <c r="C65" s="7" t="n"/>
-      <c r="D65" s="7" t="n"/>
-      <c r="E65" s="7" t="n"/>
+      <c r="A65" s="16" t="n"/>
+      <c r="B65" s="16" t="n"/>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="16" t="n"/>
       <c r="F65" s="8" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="8" t="n"/>
@@ -2031,17 +2134,17 @@
       <c r="M65" s="8" t="n"/>
       <c r="N65" s="8" t="n"/>
       <c r="O65" s="8" t="n"/>
-      <c r="P65" s="9" t="n"/>
-      <c r="Q65" s="9" t="n"/>
+      <c r="P65" s="17" t="n"/>
+      <c r="Q65" s="17" t="n"/>
       <c r="R65" s="8" t="n"/>
       <c r="S65" s="8" t="n"/>
     </row>
     <row r="66" ht="16" customHeight="1">
-      <c r="A66" s="7" t="n"/>
-      <c r="B66" s="7" t="n"/>
-      <c r="C66" s="7" t="n"/>
-      <c r="D66" s="7" t="n"/>
-      <c r="E66" s="7" t="n"/>
+      <c r="A66" s="16" t="n"/>
+      <c r="B66" s="16" t="n"/>
+      <c r="C66" s="16" t="n"/>
+      <c r="D66" s="16" t="n"/>
+      <c r="E66" s="16" t="n"/>
       <c r="F66" s="8" t="n"/>
       <c r="G66" s="8" t="n"/>
       <c r="H66" s="8" t="n"/>
@@ -2052,17 +2155,17 @@
       <c r="M66" s="8" t="n"/>
       <c r="N66" s="8" t="n"/>
       <c r="O66" s="8" t="n"/>
-      <c r="P66" s="9" t="n"/>
-      <c r="Q66" s="9" t="n"/>
+      <c r="P66" s="17" t="n"/>
+      <c r="Q66" s="17" t="n"/>
       <c r="R66" s="8" t="n"/>
       <c r="S66" s="8" t="n"/>
     </row>
     <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="7" t="n"/>
-      <c r="B67" s="7" t="n"/>
-      <c r="C67" s="7" t="n"/>
-      <c r="D67" s="7" t="n"/>
-      <c r="E67" s="7" t="n"/>
+      <c r="A67" s="16" t="n"/>
+      <c r="B67" s="16" t="n"/>
+      <c r="C67" s="16" t="n"/>
+      <c r="D67" s="16" t="n"/>
+      <c r="E67" s="16" t="n"/>
       <c r="F67" s="8" t="n"/>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="8" t="n"/>
@@ -2073,17 +2176,17 @@
       <c r="M67" s="8" t="n"/>
       <c r="N67" s="8" t="n"/>
       <c r="O67" s="8" t="n"/>
-      <c r="P67" s="9" t="n"/>
-      <c r="Q67" s="9" t="n"/>
+      <c r="P67" s="17" t="n"/>
+      <c r="Q67" s="17" t="n"/>
       <c r="R67" s="8" t="n"/>
       <c r="S67" s="8" t="n"/>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="7" t="n"/>
-      <c r="B68" s="7" t="n"/>
-      <c r="C68" s="7" t="n"/>
-      <c r="D68" s="7" t="n"/>
-      <c r="E68" s="7" t="n"/>
+      <c r="A68" s="16" t="n"/>
+      <c r="B68" s="16" t="n"/>
+      <c r="C68" s="16" t="n"/>
+      <c r="D68" s="16" t="n"/>
+      <c r="E68" s="16" t="n"/>
       <c r="F68" s="8" t="n"/>
       <c r="G68" s="8" t="n"/>
       <c r="H68" s="8" t="n"/>
@@ -2094,17 +2197,17 @@
       <c r="M68" s="8" t="n"/>
       <c r="N68" s="8" t="n"/>
       <c r="O68" s="8" t="n"/>
-      <c r="P68" s="9" t="n"/>
-      <c r="Q68" s="9" t="n"/>
+      <c r="P68" s="17" t="n"/>
+      <c r="Q68" s="17" t="n"/>
       <c r="R68" s="8" t="n"/>
       <c r="S68" s="8" t="n"/>
     </row>
     <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="7" t="n"/>
-      <c r="B69" s="7" t="n"/>
-      <c r="C69" s="7" t="n"/>
-      <c r="D69" s="7" t="n"/>
-      <c r="E69" s="7" t="n"/>
+      <c r="A69" s="16" t="n"/>
+      <c r="B69" s="16" t="n"/>
+      <c r="C69" s="16" t="n"/>
+      <c r="D69" s="16" t="n"/>
+      <c r="E69" s="16" t="n"/>
       <c r="F69" s="8" t="n"/>
       <c r="G69" s="8" t="n"/>
       <c r="H69" s="8" t="n"/>
@@ -2115,17 +2218,17 @@
       <c r="M69" s="8" t="n"/>
       <c r="N69" s="8" t="n"/>
       <c r="O69" s="8" t="n"/>
-      <c r="P69" s="9" t="n"/>
-      <c r="Q69" s="9" t="n"/>
+      <c r="P69" s="17" t="n"/>
+      <c r="Q69" s="17" t="n"/>
       <c r="R69" s="8" t="n"/>
       <c r="S69" s="8" t="n"/>
     </row>
     <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="7" t="n"/>
-      <c r="B70" s="7" t="n"/>
-      <c r="C70" s="7" t="n"/>
-      <c r="D70" s="7" t="n"/>
-      <c r="E70" s="7" t="n"/>
+      <c r="A70" s="16" t="n"/>
+      <c r="B70" s="16" t="n"/>
+      <c r="C70" s="16" t="n"/>
+      <c r="D70" s="16" t="n"/>
+      <c r="E70" s="16" t="n"/>
       <c r="F70" s="8" t="n"/>
       <c r="G70" s="8" t="n"/>
       <c r="H70" s="8" t="n"/>
@@ -2136,17 +2239,17 @@
       <c r="M70" s="8" t="n"/>
       <c r="N70" s="8" t="n"/>
       <c r="O70" s="8" t="n"/>
-      <c r="P70" s="9" t="n"/>
-      <c r="Q70" s="9" t="n"/>
+      <c r="P70" s="17" t="n"/>
+      <c r="Q70" s="17" t="n"/>
       <c r="R70" s="8" t="n"/>
       <c r="S70" s="8" t="n"/>
     </row>
     <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="7" t="n"/>
-      <c r="B71" s="7" t="n"/>
-      <c r="C71" s="7" t="n"/>
-      <c r="D71" s="7" t="n"/>
-      <c r="E71" s="7" t="n"/>
+      <c r="A71" s="16" t="n"/>
+      <c r="B71" s="16" t="n"/>
+      <c r="C71" s="16" t="n"/>
+      <c r="D71" s="16" t="n"/>
+      <c r="E71" s="16" t="n"/>
       <c r="F71" s="8" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="8" t="n"/>
@@ -2157,17 +2260,17 @@
       <c r="M71" s="8" t="n"/>
       <c r="N71" s="8" t="n"/>
       <c r="O71" s="8" t="n"/>
-      <c r="P71" s="9" t="n"/>
-      <c r="Q71" s="9" t="n"/>
+      <c r="P71" s="17" t="n"/>
+      <c r="Q71" s="17" t="n"/>
       <c r="R71" s="8" t="n"/>
       <c r="S71" s="8" t="n"/>
     </row>
     <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="7" t="n"/>
-      <c r="B72" s="7" t="n"/>
-      <c r="C72" s="7" t="n"/>
-      <c r="D72" s="7" t="n"/>
-      <c r="E72" s="7" t="n"/>
+      <c r="A72" s="16" t="n"/>
+      <c r="B72" s="16" t="n"/>
+      <c r="C72" s="16" t="n"/>
+      <c r="D72" s="16" t="n"/>
+      <c r="E72" s="16" t="n"/>
       <c r="F72" s="8" t="n"/>
       <c r="G72" s="8" t="n"/>
       <c r="H72" s="8" t="n"/>
@@ -2178,17 +2281,17 @@
       <c r="M72" s="8" t="n"/>
       <c r="N72" s="8" t="n"/>
       <c r="O72" s="8" t="n"/>
-      <c r="P72" s="9" t="n"/>
-      <c r="Q72" s="9" t="n"/>
+      <c r="P72" s="17" t="n"/>
+      <c r="Q72" s="17" t="n"/>
       <c r="R72" s="8" t="n"/>
       <c r="S72" s="8" t="n"/>
     </row>
     <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="7" t="n"/>
-      <c r="B73" s="7" t="n"/>
-      <c r="C73" s="7" t="n"/>
-      <c r="D73" s="7" t="n"/>
-      <c r="E73" s="7" t="n"/>
+      <c r="A73" s="16" t="n"/>
+      <c r="B73" s="16" t="n"/>
+      <c r="C73" s="16" t="n"/>
+      <c r="D73" s="16" t="n"/>
+      <c r="E73" s="16" t="n"/>
       <c r="F73" s="8" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="8" t="n"/>
@@ -2199,17 +2302,17 @@
       <c r="M73" s="8" t="n"/>
       <c r="N73" s="8" t="n"/>
       <c r="O73" s="8" t="n"/>
-      <c r="P73" s="9" t="n"/>
-      <c r="Q73" s="9" t="n"/>
+      <c r="P73" s="17" t="n"/>
+      <c r="Q73" s="17" t="n"/>
       <c r="R73" s="8" t="n"/>
       <c r="S73" s="8" t="n"/>
     </row>
     <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="7" t="n"/>
-      <c r="B74" s="7" t="n"/>
-      <c r="C74" s="7" t="n"/>
-      <c r="D74" s="7" t="n"/>
-      <c r="E74" s="7" t="n"/>
+      <c r="A74" s="16" t="n"/>
+      <c r="B74" s="16" t="n"/>
+      <c r="C74" s="16" t="n"/>
+      <c r="D74" s="16" t="n"/>
+      <c r="E74" s="16" t="n"/>
       <c r="F74" s="8" t="n"/>
       <c r="G74" s="8" t="n"/>
       <c r="H74" s="8" t="n"/>
@@ -2220,17 +2323,17 @@
       <c r="M74" s="8" t="n"/>
       <c r="N74" s="8" t="n"/>
       <c r="O74" s="8" t="n"/>
-      <c r="P74" s="9" t="n"/>
-      <c r="Q74" s="9" t="n"/>
+      <c r="P74" s="17" t="n"/>
+      <c r="Q74" s="17" t="n"/>
       <c r="R74" s="8" t="n"/>
       <c r="S74" s="8" t="n"/>
     </row>
     <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="7" t="n"/>
-      <c r="B75" s="7" t="n"/>
-      <c r="C75" s="7" t="n"/>
-      <c r="D75" s="7" t="n"/>
-      <c r="E75" s="7" t="n"/>
+      <c r="A75" s="16" t="n"/>
+      <c r="B75" s="16" t="n"/>
+      <c r="C75" s="16" t="n"/>
+      <c r="D75" s="16" t="n"/>
+      <c r="E75" s="16" t="n"/>
       <c r="F75" s="8" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="8" t="n"/>
@@ -2241,17 +2344,17 @@
       <c r="M75" s="8" t="n"/>
       <c r="N75" s="8" t="n"/>
       <c r="O75" s="8" t="n"/>
-      <c r="P75" s="9" t="n"/>
-      <c r="Q75" s="9" t="n"/>
+      <c r="P75" s="17" t="n"/>
+      <c r="Q75" s="17" t="n"/>
       <c r="R75" s="8" t="n"/>
       <c r="S75" s="8" t="n"/>
     </row>
     <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="7" t="n"/>
-      <c r="B76" s="7" t="n"/>
-      <c r="C76" s="7" t="n"/>
-      <c r="D76" s="7" t="n"/>
-      <c r="E76" s="7" t="n"/>
+      <c r="A76" s="16" t="n"/>
+      <c r="B76" s="16" t="n"/>
+      <c r="C76" s="16" t="n"/>
+      <c r="D76" s="16" t="n"/>
+      <c r="E76" s="16" t="n"/>
       <c r="F76" s="8" t="n"/>
       <c r="G76" s="8" t="n"/>
       <c r="H76" s="8" t="n"/>
@@ -2262,17 +2365,17 @@
       <c r="M76" s="8" t="n"/>
       <c r="N76" s="8" t="n"/>
       <c r="O76" s="8" t="n"/>
-      <c r="P76" s="9" t="n"/>
-      <c r="Q76" s="9" t="n"/>
+      <c r="P76" s="17" t="n"/>
+      <c r="Q76" s="17" t="n"/>
       <c r="R76" s="8" t="n"/>
       <c r="S76" s="8" t="n"/>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="7" t="n"/>
-      <c r="B77" s="7" t="n"/>
-      <c r="C77" s="7" t="n"/>
-      <c r="D77" s="7" t="n"/>
-      <c r="E77" s="7" t="n"/>
+      <c r="A77" s="16" t="n"/>
+      <c r="B77" s="16" t="n"/>
+      <c r="C77" s="16" t="n"/>
+      <c r="D77" s="16" t="n"/>
+      <c r="E77" s="16" t="n"/>
       <c r="F77" s="8" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="8" t="n"/>
@@ -2283,17 +2386,17 @@
       <c r="M77" s="8" t="n"/>
       <c r="N77" s="8" t="n"/>
       <c r="O77" s="8" t="n"/>
-      <c r="P77" s="9" t="n"/>
-      <c r="Q77" s="9" t="n"/>
+      <c r="P77" s="17" t="n"/>
+      <c r="Q77" s="17" t="n"/>
       <c r="R77" s="8" t="n"/>
       <c r="S77" s="8" t="n"/>
     </row>
     <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="7" t="n"/>
-      <c r="B78" s="7" t="n"/>
-      <c r="C78" s="7" t="n"/>
-      <c r="D78" s="7" t="n"/>
-      <c r="E78" s="7" t="n"/>
+      <c r="A78" s="16" t="n"/>
+      <c r="B78" s="16" t="n"/>
+      <c r="C78" s="16" t="n"/>
+      <c r="D78" s="16" t="n"/>
+      <c r="E78" s="16" t="n"/>
       <c r="F78" s="8" t="n"/>
       <c r="G78" s="8" t="n"/>
       <c r="H78" s="8" t="n"/>
@@ -2304,17 +2407,17 @@
       <c r="M78" s="8" t="n"/>
       <c r="N78" s="8" t="n"/>
       <c r="O78" s="8" t="n"/>
-      <c r="P78" s="9" t="n"/>
-      <c r="Q78" s="9" t="n"/>
+      <c r="P78" s="17" t="n"/>
+      <c r="Q78" s="17" t="n"/>
       <c r="R78" s="8" t="n"/>
       <c r="S78" s="8" t="n"/>
     </row>
     <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="7" t="n"/>
-      <c r="B79" s="7" t="n"/>
-      <c r="C79" s="7" t="n"/>
-      <c r="D79" s="7" t="n"/>
-      <c r="E79" s="7" t="n"/>
+      <c r="A79" s="16" t="n"/>
+      <c r="B79" s="16" t="n"/>
+      <c r="C79" s="16" t="n"/>
+      <c r="D79" s="16" t="n"/>
+      <c r="E79" s="16" t="n"/>
       <c r="F79" s="8" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="8" t="n"/>
@@ -2325,17 +2428,17 @@
       <c r="M79" s="8" t="n"/>
       <c r="N79" s="8" t="n"/>
       <c r="O79" s="8" t="n"/>
-      <c r="P79" s="9" t="n"/>
-      <c r="Q79" s="9" t="n"/>
+      <c r="P79" s="17" t="n"/>
+      <c r="Q79" s="17" t="n"/>
       <c r="R79" s="8" t="n"/>
       <c r="S79" s="8" t="n"/>
     </row>
     <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="7" t="n"/>
-      <c r="B80" s="7" t="n"/>
-      <c r="C80" s="7" t="n"/>
-      <c r="D80" s="7" t="n"/>
-      <c r="E80" s="7" t="n"/>
+      <c r="A80" s="16" t="n"/>
+      <c r="B80" s="16" t="n"/>
+      <c r="C80" s="16" t="n"/>
+      <c r="D80" s="16" t="n"/>
+      <c r="E80" s="16" t="n"/>
       <c r="F80" s="8" t="n"/>
       <c r="G80" s="8" t="n"/>
       <c r="H80" s="8" t="n"/>
@@ -2346,17 +2449,17 @@
       <c r="M80" s="8" t="n"/>
       <c r="N80" s="8" t="n"/>
       <c r="O80" s="8" t="n"/>
-      <c r="P80" s="9" t="n"/>
-      <c r="Q80" s="9" t="n"/>
+      <c r="P80" s="17" t="n"/>
+      <c r="Q80" s="17" t="n"/>
       <c r="R80" s="8" t="n"/>
       <c r="S80" s="8" t="n"/>
     </row>
     <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="7" t="n"/>
-      <c r="B81" s="7" t="n"/>
-      <c r="C81" s="7" t="n"/>
-      <c r="D81" s="7" t="n"/>
-      <c r="E81" s="7" t="n"/>
+      <c r="A81" s="16" t="n"/>
+      <c r="B81" s="16" t="n"/>
+      <c r="C81" s="16" t="n"/>
+      <c r="D81" s="16" t="n"/>
+      <c r="E81" s="16" t="n"/>
       <c r="F81" s="8" t="n"/>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="8" t="n"/>
@@ -2367,17 +2470,17 @@
       <c r="M81" s="8" t="n"/>
       <c r="N81" s="8" t="n"/>
       <c r="O81" s="8" t="n"/>
-      <c r="P81" s="9" t="n"/>
-      <c r="Q81" s="9" t="n"/>
+      <c r="P81" s="17" t="n"/>
+      <c r="Q81" s="17" t="n"/>
       <c r="R81" s="8" t="n"/>
       <c r="S81" s="8" t="n"/>
     </row>
     <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="7" t="n"/>
-      <c r="B82" s="7" t="n"/>
-      <c r="C82" s="7" t="n"/>
-      <c r="D82" s="7" t="n"/>
-      <c r="E82" s="7" t="n"/>
+      <c r="A82" s="16" t="n"/>
+      <c r="B82" s="16" t="n"/>
+      <c r="C82" s="16" t="n"/>
+      <c r="D82" s="16" t="n"/>
+      <c r="E82" s="16" t="n"/>
       <c r="F82" s="8" t="n"/>
       <c r="G82" s="8" t="n"/>
       <c r="H82" s="8" t="n"/>
@@ -2388,17 +2491,17 @@
       <c r="M82" s="8" t="n"/>
       <c r="N82" s="8" t="n"/>
       <c r="O82" s="8" t="n"/>
-      <c r="P82" s="9" t="n"/>
-      <c r="Q82" s="9" t="n"/>
+      <c r="P82" s="17" t="n"/>
+      <c r="Q82" s="17" t="n"/>
       <c r="R82" s="8" t="n"/>
       <c r="S82" s="8" t="n"/>
     </row>
     <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="7" t="n"/>
-      <c r="B83" s="7" t="n"/>
-      <c r="C83" s="7" t="n"/>
-      <c r="D83" s="7" t="n"/>
-      <c r="E83" s="7" t="n"/>
+      <c r="A83" s="16" t="n"/>
+      <c r="B83" s="16" t="n"/>
+      <c r="C83" s="16" t="n"/>
+      <c r="D83" s="16" t="n"/>
+      <c r="E83" s="16" t="n"/>
       <c r="F83" s="8" t="n"/>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="8" t="n"/>
@@ -2409,17 +2512,17 @@
       <c r="M83" s="8" t="n"/>
       <c r="N83" s="8" t="n"/>
       <c r="O83" s="8" t="n"/>
-      <c r="P83" s="9" t="n"/>
-      <c r="Q83" s="9" t="n"/>
+      <c r="P83" s="17" t="n"/>
+      <c r="Q83" s="17" t="n"/>
       <c r="R83" s="8" t="n"/>
       <c r="S83" s="8" t="n"/>
     </row>
     <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="7" t="n"/>
-      <c r="B84" s="7" t="n"/>
-      <c r="C84" s="7" t="n"/>
-      <c r="D84" s="7" t="n"/>
-      <c r="E84" s="7" t="n"/>
+      <c r="A84" s="16" t="n"/>
+      <c r="B84" s="16" t="n"/>
+      <c r="C84" s="16" t="n"/>
+      <c r="D84" s="16" t="n"/>
+      <c r="E84" s="16" t="n"/>
       <c r="F84" s="8" t="n"/>
       <c r="G84" s="8" t="n"/>
       <c r="H84" s="8" t="n"/>
@@ -2430,17 +2533,17 @@
       <c r="M84" s="8" t="n"/>
       <c r="N84" s="8" t="n"/>
       <c r="O84" s="8" t="n"/>
-      <c r="P84" s="9" t="n"/>
-      <c r="Q84" s="9" t="n"/>
+      <c r="P84" s="17" t="n"/>
+      <c r="Q84" s="17" t="n"/>
       <c r="R84" s="8" t="n"/>
       <c r="S84" s="8" t="n"/>
     </row>
     <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="7" t="n"/>
-      <c r="B85" s="7" t="n"/>
-      <c r="C85" s="7" t="n"/>
-      <c r="D85" s="7" t="n"/>
-      <c r="E85" s="7" t="n"/>
+      <c r="A85" s="16" t="n"/>
+      <c r="B85" s="16" t="n"/>
+      <c r="C85" s="16" t="n"/>
+      <c r="D85" s="16" t="n"/>
+      <c r="E85" s="16" t="n"/>
       <c r="F85" s="8" t="n"/>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="8" t="n"/>
@@ -2451,17 +2554,17 @@
       <c r="M85" s="8" t="n"/>
       <c r="N85" s="8" t="n"/>
       <c r="O85" s="8" t="n"/>
-      <c r="P85" s="9" t="n"/>
-      <c r="Q85" s="9" t="n"/>
+      <c r="P85" s="17" t="n"/>
+      <c r="Q85" s="17" t="n"/>
       <c r="R85" s="8" t="n"/>
       <c r="S85" s="8" t="n"/>
     </row>
     <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="7" t="n"/>
-      <c r="B86" s="7" t="n"/>
-      <c r="C86" s="7" t="n"/>
-      <c r="D86" s="7" t="n"/>
-      <c r="E86" s="7" t="n"/>
+      <c r="A86" s="16" t="n"/>
+      <c r="B86" s="16" t="n"/>
+      <c r="C86" s="16" t="n"/>
+      <c r="D86" s="16" t="n"/>
+      <c r="E86" s="16" t="n"/>
       <c r="F86" s="8" t="n"/>
       <c r="G86" s="8" t="n"/>
       <c r="H86" s="8" t="n"/>
@@ -2472,17 +2575,17 @@
       <c r="M86" s="8" t="n"/>
       <c r="N86" s="8" t="n"/>
       <c r="O86" s="8" t="n"/>
-      <c r="P86" s="9" t="n"/>
-      <c r="Q86" s="9" t="n"/>
+      <c r="P86" s="17" t="n"/>
+      <c r="Q86" s="17" t="n"/>
       <c r="R86" s="8" t="n"/>
       <c r="S86" s="8" t="n"/>
     </row>
     <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="7" t="n"/>
-      <c r="B87" s="7" t="n"/>
-      <c r="C87" s="7" t="n"/>
-      <c r="D87" s="7" t="n"/>
-      <c r="E87" s="7" t="n"/>
+      <c r="A87" s="16" t="n"/>
+      <c r="B87" s="16" t="n"/>
+      <c r="C87" s="16" t="n"/>
+      <c r="D87" s="16" t="n"/>
+      <c r="E87" s="16" t="n"/>
       <c r="F87" s="8" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="8" t="n"/>
@@ -2493,17 +2596,17 @@
       <c r="M87" s="8" t="n"/>
       <c r="N87" s="8" t="n"/>
       <c r="O87" s="8" t="n"/>
-      <c r="P87" s="9" t="n"/>
-      <c r="Q87" s="9" t="n"/>
+      <c r="P87" s="17" t="n"/>
+      <c r="Q87" s="17" t="n"/>
       <c r="R87" s="8" t="n"/>
       <c r="S87" s="8" t="n"/>
     </row>
     <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="7" t="n"/>
-      <c r="B88" s="7" t="n"/>
-      <c r="C88" s="7" t="n"/>
-      <c r="D88" s="7" t="n"/>
-      <c r="E88" s="7" t="n"/>
+      <c r="A88" s="16" t="n"/>
+      <c r="B88" s="16" t="n"/>
+      <c r="C88" s="16" t="n"/>
+      <c r="D88" s="16" t="n"/>
+      <c r="E88" s="16" t="n"/>
       <c r="F88" s="8" t="n"/>
       <c r="G88" s="8" t="n"/>
       <c r="H88" s="8" t="n"/>
@@ -2514,17 +2617,17 @@
       <c r="M88" s="8" t="n"/>
       <c r="N88" s="8" t="n"/>
       <c r="O88" s="8" t="n"/>
-      <c r="P88" s="9" t="n"/>
-      <c r="Q88" s="9" t="n"/>
+      <c r="P88" s="17" t="n"/>
+      <c r="Q88" s="17" t="n"/>
       <c r="R88" s="8" t="n"/>
       <c r="S88" s="8" t="n"/>
     </row>
     <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="7" t="n"/>
-      <c r="B89" s="7" t="n"/>
-      <c r="C89" s="7" t="n"/>
-      <c r="D89" s="7" t="n"/>
-      <c r="E89" s="7" t="n"/>
+      <c r="A89" s="16" t="n"/>
+      <c r="B89" s="16" t="n"/>
+      <c r="C89" s="16" t="n"/>
+      <c r="D89" s="16" t="n"/>
+      <c r="E89" s="16" t="n"/>
       <c r="F89" s="8" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="8" t="n"/>
@@ -2535,17 +2638,17 @@
       <c r="M89" s="8" t="n"/>
       <c r="N89" s="8" t="n"/>
       <c r="O89" s="8" t="n"/>
-      <c r="P89" s="9" t="n"/>
-      <c r="Q89" s="9" t="n"/>
+      <c r="P89" s="17" t="n"/>
+      <c r="Q89" s="17" t="n"/>
       <c r="R89" s="8" t="n"/>
       <c r="S89" s="8" t="n"/>
     </row>
     <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="7" t="n"/>
-      <c r="B90" s="7" t="n"/>
-      <c r="C90" s="7" t="n"/>
-      <c r="D90" s="7" t="n"/>
-      <c r="E90" s="7" t="n"/>
+      <c r="A90" s="16" t="n"/>
+      <c r="B90" s="16" t="n"/>
+      <c r="C90" s="16" t="n"/>
+      <c r="D90" s="16" t="n"/>
+      <c r="E90" s="16" t="n"/>
       <c r="F90" s="8" t="n"/>
       <c r="G90" s="8" t="n"/>
       <c r="H90" s="8" t="n"/>
@@ -2556,17 +2659,17 @@
       <c r="M90" s="8" t="n"/>
       <c r="N90" s="8" t="n"/>
       <c r="O90" s="8" t="n"/>
-      <c r="P90" s="9" t="n"/>
-      <c r="Q90" s="9" t="n"/>
+      <c r="P90" s="17" t="n"/>
+      <c r="Q90" s="17" t="n"/>
       <c r="R90" s="8" t="n"/>
       <c r="S90" s="8" t="n"/>
     </row>
     <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="7" t="n"/>
-      <c r="B91" s="7" t="n"/>
-      <c r="C91" s="7" t="n"/>
-      <c r="D91" s="7" t="n"/>
-      <c r="E91" s="7" t="n"/>
+      <c r="A91" s="16" t="n"/>
+      <c r="B91" s="16" t="n"/>
+      <c r="C91" s="16" t="n"/>
+      <c r="D91" s="16" t="n"/>
+      <c r="E91" s="16" t="n"/>
       <c r="F91" s="8" t="n"/>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="8" t="n"/>
@@ -2577,17 +2680,17 @@
       <c r="M91" s="8" t="n"/>
       <c r="N91" s="8" t="n"/>
       <c r="O91" s="8" t="n"/>
-      <c r="P91" s="9" t="n"/>
-      <c r="Q91" s="9" t="n"/>
+      <c r="P91" s="17" t="n"/>
+      <c r="Q91" s="17" t="n"/>
       <c r="R91" s="8" t="n"/>
       <c r="S91" s="8" t="n"/>
     </row>
     <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="7" t="n"/>
-      <c r="B92" s="7" t="n"/>
-      <c r="C92" s="7" t="n"/>
-      <c r="D92" s="7" t="n"/>
-      <c r="E92" s="7" t="n"/>
+      <c r="A92" s="16" t="n"/>
+      <c r="B92" s="16" t="n"/>
+      <c r="C92" s="16" t="n"/>
+      <c r="D92" s="16" t="n"/>
+      <c r="E92" s="16" t="n"/>
       <c r="F92" s="8" t="n"/>
       <c r="G92" s="8" t="n"/>
       <c r="H92" s="8" t="n"/>
@@ -2598,17 +2701,17 @@
       <c r="M92" s="8" t="n"/>
       <c r="N92" s="8" t="n"/>
       <c r="O92" s="8" t="n"/>
-      <c r="P92" s="9" t="n"/>
-      <c r="Q92" s="9" t="n"/>
+      <c r="P92" s="17" t="n"/>
+      <c r="Q92" s="17" t="n"/>
       <c r="R92" s="8" t="n"/>
       <c r="S92" s="8" t="n"/>
     </row>
     <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="7" t="n"/>
-      <c r="B93" s="7" t="n"/>
-      <c r="C93" s="7" t="n"/>
-      <c r="D93" s="7" t="n"/>
-      <c r="E93" s="7" t="n"/>
+      <c r="A93" s="16" t="n"/>
+      <c r="B93" s="16" t="n"/>
+      <c r="C93" s="16" t="n"/>
+      <c r="D93" s="16" t="n"/>
+      <c r="E93" s="16" t="n"/>
       <c r="F93" s="8" t="n"/>
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="8" t="n"/>
@@ -2619,17 +2722,17 @@
       <c r="M93" s="8" t="n"/>
       <c r="N93" s="8" t="n"/>
       <c r="O93" s="8" t="n"/>
-      <c r="P93" s="9" t="n"/>
-      <c r="Q93" s="9" t="n"/>
+      <c r="P93" s="17" t="n"/>
+      <c r="Q93" s="17" t="n"/>
       <c r="R93" s="8" t="n"/>
       <c r="S93" s="8" t="n"/>
     </row>
     <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="7" t="n"/>
-      <c r="B94" s="7" t="n"/>
-      <c r="C94" s="7" t="n"/>
-      <c r="D94" s="7" t="n"/>
-      <c r="E94" s="7" t="n"/>
+      <c r="A94" s="16" t="n"/>
+      <c r="B94" s="16" t="n"/>
+      <c r="C94" s="16" t="n"/>
+      <c r="D94" s="16" t="n"/>
+      <c r="E94" s="16" t="n"/>
       <c r="F94" s="8" t="n"/>
       <c r="G94" s="8" t="n"/>
       <c r="H94" s="8" t="n"/>
@@ -2640,17 +2743,17 @@
       <c r="M94" s="8" t="n"/>
       <c r="N94" s="8" t="n"/>
       <c r="O94" s="8" t="n"/>
-      <c r="P94" s="9" t="n"/>
-      <c r="Q94" s="9" t="n"/>
+      <c r="P94" s="17" t="n"/>
+      <c r="Q94" s="17" t="n"/>
       <c r="R94" s="8" t="n"/>
       <c r="S94" s="8" t="n"/>
     </row>
     <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="7" t="n"/>
-      <c r="B95" s="7" t="n"/>
-      <c r="C95" s="7" t="n"/>
-      <c r="D95" s="7" t="n"/>
-      <c r="E95" s="7" t="n"/>
+      <c r="A95" s="16" t="n"/>
+      <c r="B95" s="16" t="n"/>
+      <c r="C95" s="16" t="n"/>
+      <c r="D95" s="16" t="n"/>
+      <c r="E95" s="16" t="n"/>
       <c r="F95" s="8" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="8" t="n"/>
@@ -2661,17 +2764,17 @@
       <c r="M95" s="8" t="n"/>
       <c r="N95" s="8" t="n"/>
       <c r="O95" s="8" t="n"/>
-      <c r="P95" s="9" t="n"/>
-      <c r="Q95" s="9" t="n"/>
+      <c r="P95" s="17" t="n"/>
+      <c r="Q95" s="17" t="n"/>
       <c r="R95" s="8" t="n"/>
       <c r="S95" s="8" t="n"/>
     </row>
     <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="7" t="n"/>
-      <c r="B96" s="7" t="n"/>
-      <c r="C96" s="7" t="n"/>
-      <c r="D96" s="7" t="n"/>
-      <c r="E96" s="7" t="n"/>
+      <c r="A96" s="16" t="n"/>
+      <c r="B96" s="16" t="n"/>
+      <c r="C96" s="16" t="n"/>
+      <c r="D96" s="16" t="n"/>
+      <c r="E96" s="16" t="n"/>
       <c r="F96" s="8" t="n"/>
       <c r="G96" s="8" t="n"/>
       <c r="H96" s="8" t="n"/>
@@ -2682,17 +2785,17 @@
       <c r="M96" s="8" t="n"/>
       <c r="N96" s="8" t="n"/>
       <c r="O96" s="8" t="n"/>
-      <c r="P96" s="9" t="n"/>
-      <c r="Q96" s="9" t="n"/>
+      <c r="P96" s="17" t="n"/>
+      <c r="Q96" s="17" t="n"/>
       <c r="R96" s="8" t="n"/>
       <c r="S96" s="8" t="n"/>
     </row>
     <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="7" t="n"/>
-      <c r="B97" s="7" t="n"/>
-      <c r="C97" s="7" t="n"/>
-      <c r="D97" s="7" t="n"/>
-      <c r="E97" s="7" t="n"/>
+      <c r="A97" s="16" t="n"/>
+      <c r="B97" s="16" t="n"/>
+      <c r="C97" s="16" t="n"/>
+      <c r="D97" s="16" t="n"/>
+      <c r="E97" s="16" t="n"/>
       <c r="F97" s="8" t="n"/>
       <c r="G97" s="8" t="n"/>
       <c r="H97" s="8" t="n"/>
@@ -2703,17 +2806,17 @@
       <c r="M97" s="8" t="n"/>
       <c r="N97" s="8" t="n"/>
       <c r="O97" s="8" t="n"/>
-      <c r="P97" s="9" t="n"/>
-      <c r="Q97" s="9" t="n"/>
+      <c r="P97" s="17" t="n"/>
+      <c r="Q97" s="17" t="n"/>
       <c r="R97" s="8" t="n"/>
       <c r="S97" s="8" t="n"/>
     </row>
     <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="7" t="n"/>
-      <c r="B98" s="7" t="n"/>
-      <c r="C98" s="7" t="n"/>
-      <c r="D98" s="7" t="n"/>
-      <c r="E98" s="7" t="n"/>
+      <c r="A98" s="16" t="n"/>
+      <c r="B98" s="16" t="n"/>
+      <c r="C98" s="16" t="n"/>
+      <c r="D98" s="16" t="n"/>
+      <c r="E98" s="16" t="n"/>
       <c r="F98" s="8" t="n"/>
       <c r="G98" s="8" t="n"/>
       <c r="H98" s="8" t="n"/>
@@ -2724,17 +2827,17 @@
       <c r="M98" s="8" t="n"/>
       <c r="N98" s="8" t="n"/>
       <c r="O98" s="8" t="n"/>
-      <c r="P98" s="9" t="n"/>
-      <c r="Q98" s="9" t="n"/>
+      <c r="P98" s="17" t="n"/>
+      <c r="Q98" s="17" t="n"/>
       <c r="R98" s="8" t="n"/>
       <c r="S98" s="8" t="n"/>
     </row>
     <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="7" t="n"/>
-      <c r="B99" s="7" t="n"/>
-      <c r="C99" s="7" t="n"/>
-      <c r="D99" s="7" t="n"/>
-      <c r="E99" s="7" t="n"/>
+      <c r="A99" s="16" t="n"/>
+      <c r="B99" s="16" t="n"/>
+      <c r="C99" s="16" t="n"/>
+      <c r="D99" s="16" t="n"/>
+      <c r="E99" s="16" t="n"/>
       <c r="F99" s="8" t="n"/>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="8" t="n"/>
@@ -2745,17 +2848,17 @@
       <c r="M99" s="8" t="n"/>
       <c r="N99" s="8" t="n"/>
       <c r="O99" s="8" t="n"/>
-      <c r="P99" s="9" t="n"/>
-      <c r="Q99" s="9" t="n"/>
+      <c r="P99" s="17" t="n"/>
+      <c r="Q99" s="17" t="n"/>
       <c r="R99" s="8" t="n"/>
       <c r="S99" s="8" t="n"/>
     </row>
     <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="7" t="n"/>
-      <c r="B100" s="7" t="n"/>
-      <c r="C100" s="7" t="n"/>
-      <c r="D100" s="7" t="n"/>
-      <c r="E100" s="7" t="n"/>
+      <c r="A100" s="16" t="n"/>
+      <c r="B100" s="16" t="n"/>
+      <c r="C100" s="16" t="n"/>
+      <c r="D100" s="16" t="n"/>
+      <c r="E100" s="16" t="n"/>
       <c r="F100" s="8" t="n"/>
       <c r="G100" s="8" t="n"/>
       <c r="H100" s="8" t="n"/>
@@ -2766,17 +2869,17 @@
       <c r="M100" s="8" t="n"/>
       <c r="N100" s="8" t="n"/>
       <c r="O100" s="8" t="n"/>
-      <c r="P100" s="9" t="n"/>
-      <c r="Q100" s="9" t="n"/>
+      <c r="P100" s="17" t="n"/>
+      <c r="Q100" s="17" t="n"/>
       <c r="R100" s="8" t="n"/>
       <c r="S100" s="8" t="n"/>
     </row>
     <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="7" t="n"/>
-      <c r="B101" s="7" t="n"/>
-      <c r="C101" s="7" t="n"/>
-      <c r="D101" s="7" t="n"/>
-      <c r="E101" s="7" t="n"/>
+      <c r="A101" s="16" t="n"/>
+      <c r="B101" s="16" t="n"/>
+      <c r="C101" s="16" t="n"/>
+      <c r="D101" s="16" t="n"/>
+      <c r="E101" s="16" t="n"/>
       <c r="F101" s="8" t="n"/>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="8" t="n"/>
@@ -2787,17 +2890,17 @@
       <c r="M101" s="8" t="n"/>
       <c r="N101" s="8" t="n"/>
       <c r="O101" s="8" t="n"/>
-      <c r="P101" s="9" t="n"/>
-      <c r="Q101" s="9" t="n"/>
+      <c r="P101" s="17" t="n"/>
+      <c r="Q101" s="17" t="n"/>
       <c r="R101" s="8" t="n"/>
       <c r="S101" s="8" t="n"/>
     </row>
     <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="7" t="n"/>
-      <c r="B102" s="7" t="n"/>
-      <c r="C102" s="7" t="n"/>
-      <c r="D102" s="7" t="n"/>
-      <c r="E102" s="7" t="n"/>
+      <c r="A102" s="16" t="n"/>
+      <c r="B102" s="16" t="n"/>
+      <c r="C102" s="16" t="n"/>
+      <c r="D102" s="16" t="n"/>
+      <c r="E102" s="16" t="n"/>
       <c r="F102" s="8" t="n"/>
       <c r="G102" s="8" t="n"/>
       <c r="H102" s="8" t="n"/>
@@ -2808,17 +2911,17 @@
       <c r="M102" s="8" t="n"/>
       <c r="N102" s="8" t="n"/>
       <c r="O102" s="8" t="n"/>
-      <c r="P102" s="9" t="n"/>
-      <c r="Q102" s="9" t="n"/>
+      <c r="P102" s="17" t="n"/>
+      <c r="Q102" s="17" t="n"/>
       <c r="R102" s="8" t="n"/>
       <c r="S102" s="8" t="n"/>
     </row>
     <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="7" t="n"/>
-      <c r="B103" s="7" t="n"/>
-      <c r="C103" s="7" t="n"/>
-      <c r="D103" s="7" t="n"/>
-      <c r="E103" s="7" t="n"/>
+      <c r="A103" s="16" t="n"/>
+      <c r="B103" s="16" t="n"/>
+      <c r="C103" s="16" t="n"/>
+      <c r="D103" s="16" t="n"/>
+      <c r="E103" s="16" t="n"/>
       <c r="F103" s="8" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="8" t="n"/>
@@ -2829,17 +2932,17 @@
       <c r="M103" s="8" t="n"/>
       <c r="N103" s="8" t="n"/>
       <c r="O103" s="8" t="n"/>
-      <c r="P103" s="9" t="n"/>
-      <c r="Q103" s="9" t="n"/>
+      <c r="P103" s="17" t="n"/>
+      <c r="Q103" s="17" t="n"/>
       <c r="R103" s="8" t="n"/>
       <c r="S103" s="8" t="n"/>
     </row>
     <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="7" t="n"/>
-      <c r="B104" s="7" t="n"/>
-      <c r="C104" s="7" t="n"/>
-      <c r="D104" s="7" t="n"/>
-      <c r="E104" s="7" t="n"/>
+      <c r="A104" s="16" t="n"/>
+      <c r="B104" s="16" t="n"/>
+      <c r="C104" s="16" t="n"/>
+      <c r="D104" s="16" t="n"/>
+      <c r="E104" s="16" t="n"/>
       <c r="F104" s="8" t="n"/>
       <c r="G104" s="8" t="n"/>
       <c r="H104" s="8" t="n"/>
@@ -2850,8 +2953,8 @@
       <c r="M104" s="8" t="n"/>
       <c r="N104" s="8" t="n"/>
       <c r="O104" s="8" t="n"/>
-      <c r="P104" s="9" t="n"/>
-      <c r="Q104" s="9" t="n"/>
+      <c r="P104" s="17" t="n"/>
+      <c r="Q104" s="17" t="n"/>
       <c r="R104" s="8" t="n"/>
       <c r="S104" s="8" t="n"/>
     </row>
@@ -2861,6 +2964,24 @@
           <t>Les valeurs sont restituées depuis le SIRH (ledger congés, TCONGE historisé, lots de droits). L'Excel ne recalcule aucun droit. Col O = valeur du solde par FIFO (lots historiques) | Col P = cumul valorisation mensuelle acquise sur la période | Col Q = Solde disponible × TCONGE applicable (estimation simple pour cross-check DAF).</t>
         </is>
       </c>
+      <c r="B105" s="18" t="n"/>
+      <c r="C105" s="18" t="n"/>
+      <c r="D105" s="18" t="n"/>
+      <c r="E105" s="18" t="n"/>
+      <c r="F105" s="18" t="n"/>
+      <c r="G105" s="18" t="n"/>
+      <c r="H105" s="18" t="n"/>
+      <c r="I105" s="18" t="n"/>
+      <c r="J105" s="18" t="n"/>
+      <c r="K105" s="18" t="n"/>
+      <c r="L105" s="18" t="n"/>
+      <c r="M105" s="18" t="n"/>
+      <c r="N105" s="18" t="n"/>
+      <c r="O105" s="18" t="n"/>
+      <c r="P105" s="18" t="n"/>
+      <c r="Q105" s="18" t="n"/>
+      <c r="R105" s="18" t="n"/>
+      <c r="S105" s="19" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="3">
